--- a/Membres du groupe.xlsx
+++ b/Membres du groupe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\MonBureau\AF ISE 1 CL\Projet statistique sous R\Projet ISE1\Questionnaire-enquete-avec-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81328617-70C9-49B5-8691-D54FC35B2AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F5485D-DE21-4626-9858-DED6129726A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
